--- a/r4-core-80-include-testscripts/StructureDefinition-at-core-ext-address-municipalityCode.xlsx
+++ b/r4-core-80-include-testscripts/StructureDefinition-at-core-ext-address-municipalityCode.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T09:33:46+00:00</t>
+    <t>2026-10-08T12:29:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-80-include-testscripts/StructureDefinition-at-core-ext-address-municipalityCode.xlsx
+++ b/r4-core-80-include-testscripts/StructureDefinition-at-core-ext-address-municipalityCode.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T12:29:43+00:00</t>
+    <t>2026-10-09T05:46:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-80-include-testscripts/StructureDefinition-at-core-ext-address-municipalityCode.xlsx
+++ b/r4-core-80-include-testscripts/StructureDefinition-at-core-ext-address-municipalityCode.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T05:46:29+00:00</t>
+    <t>2026-10-09T07:37:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-80-include-testscripts/StructureDefinition-at-core-ext-address-municipalityCode.xlsx
+++ b/r4-core-80-include-testscripts/StructureDefinition-at-core-ext-address-municipalityCode.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T07:37:44+00:00</t>
+    <t>2026-10-09T10:16:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-80-include-testscripts/StructureDefinition-at-core-ext-address-municipalityCode.xlsx
+++ b/r4-core-80-include-testscripts/StructureDefinition-at-core-ext-address-municipalityCode.xlsx
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Address Municipality Code</t>
+    <t>Address Municipality Code (Gemeindecode)</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T10:16:42+00:00</t>
+    <t>2026-10-15T08:45:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>HL7® Austria FHIR® Core Extension for the municipality code part of the Austrian address</t>
+    <t>HL7® Austria FHIR® Core Extension for the municipality code (Gemeindecode) part of the Austrian address. The municipality code is related to the [municipality key (Gemeindekennziffer)](StructureDefinition-at-core-ext-address-municipalityKey.html). While these two are generally identical, there is one notable exception: in Vienna, the municipality key (Gemeindekennziffer) is consistently 90001, whereas the municipality code (Gemeindecode) varies by district. The current list of values is provided by [Statistik Austria](https://www.statistik.at/verzeichnis/reglisten/gemliste_knz.pdf).</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/r4-core-80-include-testscripts/StructureDefinition-at-core-ext-address-municipalityCode.xlsx
+++ b/r4-core-80-include-testscripts/StructureDefinition-at-core-ext-address-municipalityCode.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T08:45:14+00:00</t>
+    <t>2026-10-15T11:23:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-80-include-testscripts/StructureDefinition-at-core-ext-address-municipalityCode.xlsx
+++ b/r4-core-80-include-testscripts/StructureDefinition-at-core-ext-address-municipalityCode.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T11:23:47+00:00</t>
+    <t>2026-10-16T06:17:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-80-include-testscripts/StructureDefinition-at-core-ext-address-municipalityCode.xlsx
+++ b/r4-core-80-include-testscripts/StructureDefinition-at-core-ext-address-municipalityCode.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T06:17:07+00:00</t>
+    <t>2026-10-16T08:44:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
